--- a/frontend/data-source/software-copyrights.xlsx
+++ b/frontend/data-source/software-copyrights.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="软件著作" sheetId="1" r:id="R31e14ffa95154809"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="软件著作" sheetId="1" r:id="R8fe53c73e7f04f54"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="0"/>
+  </x:numFmts>
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -28,6 +31,11 @@
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF2B2430"/>
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
@@ -50,7 +58,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="10">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -62,6 +70,18 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -265,12 +285,12 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="56" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="26" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="42" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="44" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="58" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="76" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="27" customHeight="1">
@@ -293,6 +313,26 @@
         <x:v>note</x:v>
       </x:c>
     </x:row>
+    <x:row r="2" ht="74" customHeight="1">
+      <x:c r="A2" s="8" t="str">
+        <x:v>software-001</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>标准驱动的集成化众测服务平台V3.0</x:v>
+      </x:c>
+      <x:c r="C2" s="8" t="str">
+        <x:v>2022SR0042472</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="E2" s="8" t="str">
+        <x:v>广东拓思软件科学园有限公司;南京慕测信息科技有限公司;上海计算机软件技术开发中心;航天中认软件测评科技(北京)有限责任公司</x:v>
+      </x:c>
+      <x:c r="F2" s="8" t="str">
+        <x:v>来源：2023年度广东省科技进步奖提名项目公示（成果与陈振宇、房春荣参与的“群智驱动众测关键技术研究及其应用”项目关联）：https://www.gdktzx.com/d/file/2023/12/b63ec1e9c01d4dc001e786a6ffe777a0.pdf</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/frontend/data-source/software-copyrights.xlsx
+++ b/frontend/data-source/software-copyrights.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="软件著作" sheetId="1" r:id="R8fe53c73e7f04f54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="软件著作" sheetId="1" r:id="R8c2bca5133c54da4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -28,18 +28,12 @@
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
-      <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Aptos"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
       <x:color rgb="FF2B2430"/>
-      <x:name val="Aptos"/>
+      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -49,6 +43,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF4F1670"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -63,25 +62,21 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="left"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+    <x:xf numFmtId="200" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -286,34 +281,34 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="42" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="46" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="58" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="76" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="58" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="27" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="4" t="str">
         <x:v>software_id</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="4" t="str">
         <x:v>software_name</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="4" t="str">
         <x:v>registration_number</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="4" t="str">
         <x:v>year</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="4" t="str">
         <x:v>owners</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="4" t="str">
         <x:v>note</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="74" customHeight="1">
+    <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="8" t="str">
         <x:v>software-001</x:v>
       </x:c>
@@ -331,6 +326,1186 @@
       </x:c>
       <x:c r="F2" s="8" t="str">
         <x:v>来源：2023年度广东省科技进步奖提名项目公示（成果与陈振宇、房春荣参与的“群智驱动众测关键技术研究及其应用”项目关联）：https://www.gdktzx.com/d/file/2023/12/b63ec1e9c01d4dc001e786a6ffe777a0.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="42" customHeight="1">
+      <x:c r="A3" s="8" t="str">
+        <x:v>software-002</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="str">
+        <x:v>慕测趋势数据电子商务精准运营分析服务系统软件</x:v>
+      </x:c>
+      <x:c r="C3" s="8" t="str">
+        <x:v>2014SR026706</x:v>
+      </x:c>
+      <x:c r="D3" s="9" t="n">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="E3" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F3" s="8" t="str">
+        <x:v>来源工作表：慕测；简称：趋势数据分析系统；型号：V1.0；开发完成时间：2013-12-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="42" customHeight="1">
+      <x:c r="A4" s="8" t="str">
+        <x:v>software-003</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="str">
+        <x:v>慕测可复用测试用例库管理系统软件</x:v>
+      </x:c>
+      <x:c r="C4" s="8" t="str">
+        <x:v>2017SR467926</x:v>
+      </x:c>
+      <x:c r="D4" s="9" t="n">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="E4" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F4" s="8" t="str">
+        <x:v>来源工作表：慕测；型号：V1.0；开发完成时间：2015-05-20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="8" t="str">
+        <x:v>software-004</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="str">
+        <x:v>慕测MT-CUBE系统软件</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="str">
+        <x:v>2018SR243184</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="E5" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F5" s="8" t="str">
+        <x:v>来源工作表：慕测；简称：MT-CUBE；型号：V1.0；开发完成时间：2018-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="8" t="str">
+        <x:v>software-005</x:v>
+      </x:c>
+      <x:c r="B6" s="8" t="str">
+        <x:v>慕测MT-MOB系统软件</x:v>
+      </x:c>
+      <x:c r="C6" s="8" t="str">
+        <x:v>2018SR243191</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="E6" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F6" s="8" t="str">
+        <x:v>来源工作表：慕测；简称：MT-MOB；型号：V1.0；开发完成时间：2016-11-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="8" t="str">
+        <x:v>software-006</x:v>
+      </x:c>
+      <x:c r="B7" s="8" t="str">
+        <x:v>慕测MT-BASE系统软件</x:v>
+      </x:c>
+      <x:c r="C7" s="8" t="str">
+        <x:v>2018SR263412</x:v>
+      </x:c>
+      <x:c r="D7" s="9" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="E7" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F7" s="8" t="str">
+        <x:v>来源工作表：慕测；简称：MT-BASE；型号：V1.0；开发完成时间：2018-01-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="8" t="str">
+        <x:v>software-007</x:v>
+      </x:c>
+      <x:c r="B8" s="8" t="str">
+        <x:v>慕测MT-DEV系统软件</x:v>
+      </x:c>
+      <x:c r="C8" s="8" t="str">
+        <x:v>2018SR270560</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="E8" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F8" s="8" t="str">
+        <x:v>来源工作表：慕测；简称：MT-DEV；型号：V1.0；开发完成时间：2017-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="8" t="str">
+        <x:v>software-008</x:v>
+      </x:c>
+      <x:c r="B9" s="8" t="str">
+        <x:v>单元测试用例规范性检查软件</x:v>
+      </x:c>
+      <x:c r="C9" s="8" t="str">
+        <x:v>2018SR549862</x:v>
+      </x:c>
+      <x:c r="D9" s="9" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="E9" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F9" s="8" t="str">
+        <x:v>来源工作表：慕测；型号：V1.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="8" t="str">
+        <x:v>software-009</x:v>
+      </x:c>
+      <x:c r="B10" s="8" t="str">
+        <x:v>Java类测试顺序分析软件</x:v>
+      </x:c>
+      <x:c r="C10" s="8" t="str">
+        <x:v>2018SR549858</x:v>
+      </x:c>
+      <x:c r="D10" s="9" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="E10" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F10" s="8" t="str">
+        <x:v>来源工作表：慕测；型号：V1.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="8" t="str">
+        <x:v>software-010</x:v>
+      </x:c>
+      <x:c r="B11" s="8" t="str">
+        <x:v>Java代码相似性度量软件</x:v>
+      </x:c>
+      <x:c r="C11" s="8" t="str">
+        <x:v>2018SR549854</x:v>
+      </x:c>
+      <x:c r="D11" s="9" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="E11" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F11" s="8" t="str">
+        <x:v>来源工作表：慕测</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="8" t="str">
+        <x:v>software-011</x:v>
+      </x:c>
+      <x:c r="B12" s="8" t="str">
+        <x:v>基于慕测平台的用户测试引导系统</x:v>
+      </x:c>
+      <x:c r="C12" s="8" t="str">
+        <x:v>2018SR549868</x:v>
+      </x:c>
+      <x:c r="D12" s="9" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="E12" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F12" s="8" t="str">
+        <x:v>来源工作表：慕测；型号：V1.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="8" t="str">
+        <x:v>software-012</x:v>
+      </x:c>
+      <x:c r="B13" s="8" t="str">
+        <x:v>数值稳定性相关安全漏洞隐患的自动化检测工具</x:v>
+      </x:c>
+      <x:c r="C13" s="8" t="str">
+        <x:v>2018SR575240</x:v>
+      </x:c>
+      <x:c r="D13" s="9" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="E13" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F13" s="8" t="str">
+        <x:v>来源工作表：慕测；型号：V1.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="8" t="str">
+        <x:v>software-013</x:v>
+      </x:c>
+      <x:c r="B14" s="8" t="str">
+        <x:v>RepoPal-GitHub相似高质量仓库推荐系统</x:v>
+      </x:c>
+      <x:c r="C14" s="8" t="str">
+        <x:v>2018SR688907</x:v>
+      </x:c>
+      <x:c r="D14" s="9" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="E14" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F14" s="8" t="str">
+        <x:v>来源工作表：慕测；简称：RepoPal；型号：V1.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="42" customHeight="1">
+      <x:c r="A15" s="8" t="str">
+        <x:v>software-014</x:v>
+      </x:c>
+      <x:c r="B15" s="8" t="str">
+        <x:v>慕测MT-CIT-BASE系统软件</x:v>
+      </x:c>
+      <x:c r="C15" s="8" t="str">
+        <x:v>2020SR1269635</x:v>
+      </x:c>
+      <x:c r="D15" s="9" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="E15" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F15" s="8" t="str">
+        <x:v>来源工作表：慕测；原登记名称：慕测开发测试一体化系统；简称：MT-DevT；型号：V1.0；开发完成时间：2020-03-06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="A16" s="8" t="str">
+        <x:v>software-015</x:v>
+      </x:c>
+      <x:c r="B16" s="8" t="str">
+        <x:v>慕测MT-FIX系统软件</x:v>
+      </x:c>
+      <x:c r="C16" s="8" t="str">
+        <x:v>2020SR1269634</x:v>
+      </x:c>
+      <x:c r="D16" s="9" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="E16" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F16" s="8" t="str">
+        <x:v>来源工作表：慕测；原登记名称：慕测安全扫描系统；简称：MT-Sec；型号：V1.0；开发完成时间：2020-03-12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="42" customHeight="1">
+      <x:c r="A17" s="8" t="str">
+        <x:v>software-016</x:v>
+      </x:c>
+      <x:c r="B17" s="8" t="str">
+        <x:v>慕测MT-AITest系统软件</x:v>
+      </x:c>
+      <x:c r="C17" s="8" t="str">
+        <x:v>2021SR0038517</x:v>
+      </x:c>
+      <x:c r="D17" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E17" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F17" s="8" t="str">
+        <x:v>来源工作表：慕测；原登记名称：慕测AI应用测试系统；简称：MT-AITest；型号：V1.0；开发完成时间：2020-01-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="A18" s="8" t="str">
+        <x:v>software-017</x:v>
+      </x:c>
+      <x:c r="B18" s="8" t="str">
+        <x:v>慕测MT-CIT-Server系统软件</x:v>
+      </x:c>
+      <x:c r="C18" s="8" t="str">
+        <x:v>2021SR0038519</x:v>
+      </x:c>
+      <x:c r="D18" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E18" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F18" s="8" t="str">
+        <x:v>来源工作表：慕测；原登记名称：慕测群体智能测试系统；简称：MT-CIT；型号：V1.0；开发完成时间：2020-02-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="42" customHeight="1">
+      <x:c r="A19" s="8" t="str">
+        <x:v>software-018</x:v>
+      </x:c>
+      <x:c r="B19" s="8" t="str">
+        <x:v>慕测MT-Report系统软件</x:v>
+      </x:c>
+      <x:c r="C19" s="8" t="str">
+        <x:v>2021SR0104732</x:v>
+      </x:c>
+      <x:c r="D19" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E19" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F19" s="8" t="str">
+        <x:v>来源工作表：慕测；原登记名称：慕测智能化测试系统；型号：V1.0；开发完成时间：2019-11-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="42" customHeight="1">
+      <x:c r="A20" s="8" t="str">
+        <x:v>software-019</x:v>
+      </x:c>
+      <x:c r="B20" s="8" t="str">
+        <x:v>慕测MT-XCode系统软件</x:v>
+      </x:c>
+      <x:c r="C20" s="8" t="str">
+        <x:v>2021SR0038509</x:v>
+      </x:c>
+      <x:c r="D20" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E20" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F20" s="8" t="str">
+        <x:v>来源工作表：慕测；原登记名称：慕测智能化编程系统；简称：MT-IDE；型号：V1.0；开发完成时间：2020-04-18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="42" customHeight="1">
+      <x:c r="A21" s="8" t="str">
+        <x:v>software-020</x:v>
+      </x:c>
+      <x:c r="B21" s="8" t="str">
+        <x:v>慕测MT-EVA系统软件</x:v>
+      </x:c>
+      <x:c r="C21" s="8" t="str">
+        <x:v>2021SR0038497</x:v>
+      </x:c>
+      <x:c r="D21" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E21" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F21" s="8" t="str">
+        <x:v>来源工作表：慕测；原登记名称：慕测软件作品自动化测评系统；型号：V1.0；开发完成时间：2020-02-22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="42" customHeight="1">
+      <x:c r="A22" s="8" t="str">
+        <x:v>software-021</x:v>
+      </x:c>
+      <x:c r="B22" s="8" t="str">
+        <x:v>慕测MT-DQM系统软件</x:v>
+      </x:c>
+      <x:c r="C22" s="8" t="str">
+        <x:v>2021SR0038508</x:v>
+      </x:c>
+      <x:c r="D22" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E22" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F22" s="8" t="str">
+        <x:v>来源工作表：慕测；原登记名称：慕测数据质量测评系统；型号：V1.0；开发完成时间：2019-06-18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="42" customHeight="1">
+      <x:c r="A23" s="8" t="str">
+        <x:v>software-022</x:v>
+      </x:c>
+      <x:c r="B23" s="8" t="str">
+        <x:v>慕测MT-MQM系统软件</x:v>
+      </x:c>
+      <x:c r="C23" s="8" t="str">
+        <x:v>2021SR0038498</x:v>
+      </x:c>
+      <x:c r="D23" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E23" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F23" s="8" t="str">
+        <x:v>来源工作表：慕测；原登记名称：慕测AI测试评估与可视化系统；型号：V1.0；开发完成时间：2019-04-20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="42" customHeight="1">
+      <x:c r="A24" s="8" t="str">
+        <x:v>software-023</x:v>
+      </x:c>
+      <x:c r="B24" s="8" t="str">
+        <x:v>慕测MT-DAU系统软件</x:v>
+      </x:c>
+      <x:c r="C24" s="8" t="str">
+        <x:v>2021SR0039554</x:v>
+      </x:c>
+      <x:c r="D24" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E24" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F24" s="8" t="str">
+        <x:v>来源工作表：慕测；原登记名称：慕测测试数据扩增系统；简称：MT-TAU；型号：V1.0；开发完成时间：2019-04-15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="42" customHeight="1">
+      <x:c r="A25" s="8" t="str">
+        <x:v>software-024</x:v>
+      </x:c>
+      <x:c r="B25" s="8" t="str">
+        <x:v>慕测MT-Web系统软件</x:v>
+      </x:c>
+      <x:c r="C25" s="8" t="str">
+        <x:v>2021SR0658487</x:v>
+      </x:c>
+      <x:c r="D25" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E25" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F25" s="8" t="str">
+        <x:v>来源工作表：慕测；原登记名称：慕测Web应用测试系统；型号：V1.0；开发完成时间：2020-01-14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="42" customHeight="1">
+      <x:c r="A26" s="8" t="str">
+        <x:v>software-025</x:v>
+      </x:c>
+      <x:c r="B26" s="8" t="str">
+        <x:v>慕测AI模糊测试系统</x:v>
+      </x:c>
+      <x:c r="C26" s="8" t="str">
+        <x:v>2021SR0658501</x:v>
+      </x:c>
+      <x:c r="D26" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E26" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F26" s="8" t="str">
+        <x:v>来源工作表：慕测；型号：V1.0；开发完成时间：2020-04-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="42" customHeight="1">
+      <x:c r="A27" s="8" t="str">
+        <x:v>software-026</x:v>
+      </x:c>
+      <x:c r="B27" s="8" t="str">
+        <x:v>慕测MT-FUZ系统软件</x:v>
+      </x:c>
+      <x:c r="C27" s="8" t="str">
+        <x:v>2021SR0293906</x:v>
+      </x:c>
+      <x:c r="D27" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E27" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F27" s="8" t="str">
+        <x:v>来源工作表：慕测；型号：V1.0；开发完成时间：2020-04-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="42" customHeight="1">
+      <x:c r="A28" s="8" t="str">
+        <x:v>software-027</x:v>
+      </x:c>
+      <x:c r="B28" s="8" t="str">
+        <x:v>慕测MT-AQUAMAN系统软件</x:v>
+      </x:c>
+      <x:c r="C28" s="8" t="str">
+        <x:v>2021SR0850673</x:v>
+      </x:c>
+      <x:c r="D28" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E28" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F28" s="8" t="str">
+        <x:v>来源工作表：慕测；型号：V1.0；开发完成时间：2021-03-25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="42" customHeight="1">
+      <x:c r="A29" s="8" t="str">
+        <x:v>software-028</x:v>
+      </x:c>
+      <x:c r="B29" s="8" t="str">
+        <x:v>慕测MT-IAI系统软件</x:v>
+      </x:c>
+      <x:c r="C29" s="8" t="str">
+        <x:v>2021SR1462589</x:v>
+      </x:c>
+      <x:c r="D29" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E29" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F29" s="8" t="str">
+        <x:v>来源工作表：慕测；开发完成时间：2021-04-30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="42" customHeight="1">
+      <x:c r="A30" s="8" t="str">
+        <x:v>software-029</x:v>
+      </x:c>
+      <x:c r="B30" s="8" t="str">
+        <x:v>慕测实验室管理系统</x:v>
+      </x:c>
+      <x:c r="C30" s="8" t="str">
+        <x:v>2022SR0310190</x:v>
+      </x:c>
+      <x:c r="D30" s="9" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="E30" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F30" s="8" t="str">
+        <x:v>来源工作表：慕测；简称：MT-LIMS；开发完成时间：2022-01-12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="42" customHeight="1">
+      <x:c r="A31" s="8" t="str">
+        <x:v>software-030</x:v>
+      </x:c>
+      <x:c r="B31" s="8" t="str">
+        <x:v>慕测MT-AUG系统软件</x:v>
+      </x:c>
+      <x:c r="C31" s="8" t="str">
+        <x:v>2022SR1575199</x:v>
+      </x:c>
+      <x:c r="D31" s="9" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="E31" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F31" s="8" t="str">
+        <x:v>来源工作表：慕测；开发完成时间：2022-05-20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="42" customHeight="1">
+      <x:c r="A32" s="8" t="str">
+        <x:v>software-031</x:v>
+      </x:c>
+      <x:c r="B32" s="8" t="str">
+        <x:v>面向APPStudio开发过程的智能化软件精准测试系统</x:v>
+      </x:c>
+      <x:c r="C32" s="8" t="str">
+        <x:v>2023SR0556081</x:v>
+      </x:c>
+      <x:c r="D32" s="9" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="E32" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F32" s="8" t="str">
+        <x:v>来源工作表：慕测；开发完成时间：2022-03-16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="42" customHeight="1">
+      <x:c r="A33" s="8" t="str">
+        <x:v>software-032</x:v>
+      </x:c>
+      <x:c r="B33" s="8" t="str">
+        <x:v>基于大模型的java单元测试生成系统</x:v>
+      </x:c>
+      <x:c r="C33" s="8" t="str">
+        <x:v>2024SR0498211</x:v>
+      </x:c>
+      <x:c r="D33" s="9" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="E33" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F33" s="8" t="str">
+        <x:v>来源工作表：慕测；开发完成时间：2023-12-30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="42" customHeight="1">
+      <x:c r="A34" s="8" t="str">
+        <x:v>software-033</x:v>
+      </x:c>
+      <x:c r="B34" s="8" t="str">
+        <x:v>基于规则和大语言模型的测试技能综合评估系统</x:v>
+      </x:c>
+      <x:c r="C34" s="8" t="str">
+        <x:v>2025SR1258531</x:v>
+      </x:c>
+      <x:c r="D34" s="9" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="E34" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F34" s="8" t="str">
+        <x:v>来源工作表：慕测；简称：MT-RUM-Test</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="42" customHeight="1">
+      <x:c r="A35" s="8" t="str">
+        <x:v>software-034</x:v>
+      </x:c>
+      <x:c r="B35" s="8" t="str">
+        <x:v>慕测教学智能管理系统</x:v>
+      </x:c>
+      <x:c r="C35" s="8" t="str">
+        <x:v>2025SR1248123</x:v>
+      </x:c>
+      <x:c r="D35" s="9" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="E35" s="8" t="str">
+        <x:v>南京慕测信息科技有限公司</x:v>
+      </x:c>
+      <x:c r="F35" s="8" t="str">
+        <x:v>来源工作表：慕测；简称：MT-Teaching</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="42" customHeight="1">
+      <x:c r="A36" s="8" t="str">
+        <x:v>software-035</x:v>
+      </x:c>
+      <x:c r="B36" s="8" t="str">
+        <x:v>慕智MI-FUZ系统软件</x:v>
+      </x:c>
+      <x:c r="C36" s="8" t="str">
+        <x:v>2020SR1855521</x:v>
+      </x:c>
+      <x:c r="D36" s="9" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="E36" s="8" t="str">
+        <x:v>深圳慕智科技有限公司</x:v>
+      </x:c>
+      <x:c r="F36" s="8" t="str">
+        <x:v>来源工作表：慕智；原登记名称：面向自动驾驶图像数据测试用例生成系统；型号：V1.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="42" customHeight="1">
+      <x:c r="A37" s="8" t="str">
+        <x:v>software-036</x:v>
+      </x:c>
+      <x:c r="B37" s="8" t="str">
+        <x:v>慕智MI-DQM系统软件</x:v>
+      </x:c>
+      <x:c r="C37" s="8" t="str">
+        <x:v>2021SR0086243</x:v>
+      </x:c>
+      <x:c r="D37" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E37" s="8" t="str">
+        <x:v>深圳慕智科技有限公司</x:v>
+      </x:c>
+      <x:c r="F37" s="8" t="str">
+        <x:v>来源工作表：慕智；原登记名称：新能源电池数据质量度量系统；型号：V1.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="42" customHeight="1">
+      <x:c r="A38" s="8" t="str">
+        <x:v>software-037</x:v>
+      </x:c>
+      <x:c r="B38" s="8" t="str">
+        <x:v>慕智MI-MQM系统软件</x:v>
+      </x:c>
+      <x:c r="C38" s="8" t="str">
+        <x:v>2021SR0086242</x:v>
+      </x:c>
+      <x:c r="D38" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E38" s="8" t="str">
+        <x:v>深圳慕智科技有限公司</x:v>
+      </x:c>
+      <x:c r="F38" s="8" t="str">
+        <x:v>来源工作表：慕智；原登记名称：面向智能交通模型正确性的蜕变测试系统；型号：V1.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="42" customHeight="1">
+      <x:c r="A39" s="8" t="str">
+        <x:v>software-038</x:v>
+      </x:c>
+      <x:c r="B39" s="8" t="str">
+        <x:v>慕智MI-DAU系统软件</x:v>
+      </x:c>
+      <x:c r="C39" s="8" t="str">
+        <x:v>2021SR0265693</x:v>
+      </x:c>
+      <x:c r="D39" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E39" s="8" t="str">
+        <x:v>深圳慕智科技有限公司</x:v>
+      </x:c>
+      <x:c r="F39" s="8" t="str">
+        <x:v>来源工作表：慕智；原登记名称：基于规则变异的自动驾驶激光雷达数据扩增系统；型号：V1.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="42" customHeight="1">
+      <x:c r="A40" s="8" t="str">
+        <x:v>software-039</x:v>
+      </x:c>
+      <x:c r="B40" s="8" t="str">
+        <x:v>慕智MI-PRD系统软件</x:v>
+      </x:c>
+      <x:c r="C40" s="8" t="str">
+        <x:v>2021SR0101030</x:v>
+      </x:c>
+      <x:c r="D40" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E40" s="8" t="str">
+        <x:v>深圳慕智科技有限公司</x:v>
+      </x:c>
+      <x:c r="F40" s="8" t="str">
+        <x:v>来源工作表：慕智；原登记名称：新能源电池寿命预测系统；型号：V1.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="42" customHeight="1">
+      <x:c r="A41" s="8" t="str">
+        <x:v>software-040</x:v>
+      </x:c>
+      <x:c r="B41" s="8" t="str">
+        <x:v>慕智MI-FIX系统软件</x:v>
+      </x:c>
+      <x:c r="C41" s="8" t="str">
+        <x:v>2021SR0211582</x:v>
+      </x:c>
+      <x:c r="D41" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E41" s="8" t="str">
+        <x:v>深圳慕智科技有限公司</x:v>
+      </x:c>
+      <x:c r="F41" s="8" t="str">
+        <x:v>来源工作表：慕智；原登记名称：新能源电池智能管控系统；型号：V1.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="42" customHeight="1">
+      <x:c r="A42" s="8" t="str">
+        <x:v>software-041</x:v>
+      </x:c>
+      <x:c r="B42" s="8" t="str">
+        <x:v>软著iOS应用GUI测试系统-2012-06-20iGTS</x:v>
+      </x:c>
+      <x:c r="C42" s="8" t="str">
+        <x:v>2013SR126366</x:v>
+      </x:c>
+      <x:c r="D42" s="9" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="E42" s="8" t="str">
+        <x:v>南京大学</x:v>
+      </x:c>
+      <x:c r="F42" s="8" t="str">
+        <x:v>来源工作表：南大</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="42" customHeight="1">
+      <x:c r="A43" s="8" t="str">
+        <x:v>software-042</x:v>
+      </x:c>
+      <x:c r="B43" s="8" t="str">
+        <x:v>软著测试用例优先级优化系统-2012-06-05TC</x:v>
+      </x:c>
+      <x:c r="C43" s="8" t="str">
+        <x:v>2013SR127950</x:v>
+      </x:c>
+      <x:c r="D43" s="9" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="E43" s="8" t="str">
+        <x:v>南京大学</x:v>
+      </x:c>
+      <x:c r="F43" s="8" t="str">
+        <x:v>来源工作表：南大；开发完成时间：2012-06-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="42" customHeight="1">
+      <x:c r="A44" s="8" t="str">
+        <x:v>software-043</x:v>
+      </x:c>
+      <x:c r="B44" s="8" t="str">
+        <x:v>软著动态网页测试覆盖检测软件-2012-06-06TestCoverTool</x:v>
+      </x:c>
+      <x:c r="C44" s="8" t="str">
+        <x:v>2013SR127462</x:v>
+      </x:c>
+      <x:c r="D44" s="9" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="E44" s="8" t="str">
+        <x:v>南京大学</x:v>
+      </x:c>
+      <x:c r="F44" s="8" t="str">
+        <x:v>来源工作表：南大；开发完成时间：2012-06-06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="42" customHeight="1">
+      <x:c r="A45" s="8" t="str">
+        <x:v>software-044</x:v>
+      </x:c>
+      <x:c r="B45" s="8" t="str">
+        <x:v>TCDA测试代码相似性分析工具系统</x:v>
+      </x:c>
+      <x:c r="C45" s="8" t="str">
+        <x:v>2018SR726369</x:v>
+      </x:c>
+      <x:c r="D45" s="9" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="E45" s="8" t="str">
+        <x:v>南京大学</x:v>
+      </x:c>
+      <x:c r="F45" s="8" t="str">
+        <x:v>来源工作表：南大</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="42" customHeight="1">
+      <x:c r="A46" s="8" t="str">
+        <x:v>software-045</x:v>
+      </x:c>
+      <x:c r="B46" s="8" t="str">
+        <x:v>安卓单元测试自动生成工具系统</x:v>
+      </x:c>
+      <x:c r="C46" s="8" t="str">
+        <x:v>2018SR726260</x:v>
+      </x:c>
+      <x:c r="D46" s="9" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="E46" s="8" t="str">
+        <x:v>南京大学</x:v>
+      </x:c>
+      <x:c r="F46" s="8" t="str">
+        <x:v>来源工作表：南大</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="42" customHeight="1">
+      <x:c r="A47" s="8" t="str">
+        <x:v>software-046</x:v>
+      </x:c>
+      <x:c r="B47" s="8" t="str">
+        <x:v>代码与模型相融合的测试系统</x:v>
+      </x:c>
+      <x:c r="C47" s="8" t="str">
+        <x:v>2018SR725966</x:v>
+      </x:c>
+      <x:c r="D47" s="9" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="E47" s="8" t="str">
+        <x:v>南京大学</x:v>
+      </x:c>
+      <x:c r="F47" s="8" t="str">
+        <x:v>来源工作表：南大</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="42" customHeight="1">
+      <x:c r="A48" s="8" t="str">
+        <x:v>software-047</x:v>
+      </x:c>
+      <x:c r="B48" s="8" t="str">
+        <x:v>软件的数值稳定性测试工具系统</x:v>
+      </x:c>
+      <x:c r="C48" s="8" t="str">
+        <x:v>2018SR725916</x:v>
+      </x:c>
+      <x:c r="D48" s="9" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="E48" s="8" t="str">
+        <x:v>南京大学</x:v>
+      </x:c>
+      <x:c r="F48" s="8" t="str">
+        <x:v>来源工作表：南大</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="42" customHeight="1">
+      <x:c r="A49" s="8" t="str">
+        <x:v>software-048</x:v>
+      </x:c>
+      <x:c r="B49" s="8" t="str">
+        <x:v>南大多样性数据驱动智能测试系统</x:v>
+      </x:c>
+      <x:c r="C49" s="8" t="str">
+        <x:v>2022SR0982369</x:v>
+      </x:c>
+      <x:c r="D49" s="9" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="E49" s="8" t="str">
+        <x:v>南京大学</x:v>
+      </x:c>
+      <x:c r="F49" s="8" t="str">
+        <x:v>来源工作表：南大；开发完成时间：2022-05-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="42" customHeight="1">
+      <x:c r="A50" s="8" t="str">
+        <x:v>software-049</x:v>
+      </x:c>
+      <x:c r="B50" s="8" t="str">
+        <x:v>南大行为分析数据驱动测试系统</x:v>
+      </x:c>
+      <x:c r="C50" s="8" t="str">
+        <x:v>2022SR1008896</x:v>
+      </x:c>
+      <x:c r="D50" s="9" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="E50" s="8" t="str">
+        <x:v>南京大学</x:v>
+      </x:c>
+      <x:c r="F50" s="8" t="str">
+        <x:v>来源工作表：南大；开发完成时间：2022-03-17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="42" customHeight="1">
+      <x:c r="A51" s="8" t="str">
+        <x:v>software-050</x:v>
+      </x:c>
+      <x:c r="B51" s="8" t="str">
+        <x:v>南大智能装备抗干扰性评测系统</x:v>
+      </x:c>
+      <x:c r="C51" s="8" t="str">
+        <x:v>2022SR0993044</x:v>
+      </x:c>
+      <x:c r="D51" s="9" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="E51" s="8" t="str">
+        <x:v>南京大学</x:v>
+      </x:c>
+      <x:c r="F51" s="8" t="str">
+        <x:v>来源工作表：南大；开发完成时间：2022-04-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="42" customHeight="1">
+      <x:c r="A52" s="8" t="str">
+        <x:v>software-051</x:v>
+      </x:c>
+      <x:c r="B52" s="8" t="str">
+        <x:v>神经网络测试数据优先级度量系统</x:v>
+      </x:c>
+      <x:c r="C52" s="8" t="str">
+        <x:v>2022SR1008783</x:v>
+      </x:c>
+      <x:c r="D52" s="9" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="E52" s="8" t="str">
+        <x:v>南京大学</x:v>
+      </x:c>
+      <x:c r="F52" s="8" t="str">
+        <x:v>来源工作表：南大；开发完成时间：2022-04-28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="42" customHeight="1">
+      <x:c r="A53" s="8" t="str">
+        <x:v>software-052</x:v>
+      </x:c>
+      <x:c r="B53" s="8" t="str">
+        <x:v>基于场景语义的自动驾驶模型仿真测试系统V1.0</x:v>
+      </x:c>
+      <x:c r="C53" s="8" t="str">
+        <x:v>2023SR0532784</x:v>
+      </x:c>
+      <x:c r="D53" s="9" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="E53" s="8" t="str">
+        <x:v>南京大学</x:v>
+      </x:c>
+      <x:c r="F53" s="8" t="str">
+        <x:v>来源工作表：南大</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="42" customHeight="1">
+      <x:c r="A54" s="8" t="str">
+        <x:v>software-053</x:v>
+      </x:c>
+      <x:c r="B54" s="8" t="str">
+        <x:v>慕尚MS-COL系统软件</x:v>
+      </x:c>
+      <x:c r="C54" s="8" t="str">
+        <x:v>2021SR0331521</x:v>
+      </x:c>
+      <x:c r="D54" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E54" s="8" t="str">
+        <x:v>慕尚</x:v>
+      </x:c>
+      <x:c r="F54" s="8" t="str">
+        <x:v>来源工作表：慕尚；原登记名称：慕尚人机协同众测系统；型号：V1.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="42" customHeight="1">
+      <x:c r="A55" s="8" t="str">
+        <x:v>software-054</x:v>
+      </x:c>
+      <x:c r="B55" s="8" t="str">
+        <x:v>慕尚MS-IRF系统软件</x:v>
+      </x:c>
+      <x:c r="C55" s="8" t="str">
+        <x:v>2021SR1011158</x:v>
+      </x:c>
+      <x:c r="D55" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E55" s="8" t="str">
+        <x:v>慕尚</x:v>
+      </x:c>
+      <x:c r="F55" s="8" t="str">
+        <x:v>来源工作表：慕尚；原登记名称：慕尚缺陷报告融合系统；型号：V1.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="42" customHeight="1">
+      <x:c r="A56" s="8" t="str">
+        <x:v>software-055</x:v>
+      </x:c>
+      <x:c r="B56" s="8" t="str">
+        <x:v>慕尚MS-EVA系统软件</x:v>
+      </x:c>
+      <x:c r="C56" s="8" t="str">
+        <x:v>2021SR0335231</x:v>
+      </x:c>
+      <x:c r="D56" s="9" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="E56" s="8" t="str">
+        <x:v>慕尚</x:v>
+      </x:c>
+      <x:c r="F56" s="8" t="str">
+        <x:v>来源工作表：慕尚；原登记名称：慕尚风险等级预测系统；型号：V1.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="42" customHeight="1">
+      <x:c r="A57" s="8" t="str">
+        <x:v>software-056</x:v>
+      </x:c>
+      <x:c r="B57" s="8" t="str">
+        <x:v>基于色彩分析的艺术品风格识别系统</x:v>
+      </x:c>
+      <x:c r="C57" s="8" t="str">
+        <x:v>2022SR0254335</x:v>
+      </x:c>
+      <x:c r="D57" s="9" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="E57" s="8" t="str">
+        <x:v>慕德</x:v>
+      </x:c>
+      <x:c r="F57" s="8" t="str">
+        <x:v>来源工作表：慕德；开发完成时间：2021-02-04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="42" customHeight="1">
+      <x:c r="A58" s="8" t="str">
+        <x:v>software-057</x:v>
+      </x:c>
+      <x:c r="B58" s="8" t="str">
+        <x:v>安卓自动化测试工具评估系统</x:v>
+      </x:c>
+      <x:c r="C58" s="8" t="str">
+        <x:v>2022SR0939034</x:v>
+      </x:c>
+      <x:c r="D58" s="9" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="E58" s="8" t="str">
+        <x:v>陈振宇</x:v>
+      </x:c>
+      <x:c r="F58" s="8" t="str">
+        <x:v>来源工作表：陈振宇；开发完成时间：2021-08-15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="42" customHeight="1">
+      <x:c r="A59" s="8" t="str">
+        <x:v>software-058</x:v>
+      </x:c>
+      <x:c r="B59" s="8" t="str">
+        <x:v>软件测试能力多维评估系统</x:v>
+      </x:c>
+      <x:c r="C59" s="8" t="str">
+        <x:v>2022SR0950121</x:v>
+      </x:c>
+      <x:c r="D59" s="9" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="E59" s="8" t="str">
+        <x:v>陈振宇</x:v>
+      </x:c>
+      <x:c r="F59" s="8" t="str">
+        <x:v>来源工作表：陈振宇；开发完成时间：2021-04-15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="42" customHeight="1">
+      <x:c r="A60" s="8" t="str">
+        <x:v>software-059</x:v>
+      </x:c>
+      <x:c r="B60" s="8" t="str">
+        <x:v>基于蜕变关系的激光雷达点云数据扩增系统</x:v>
+      </x:c>
+      <x:c r="C60" s="8" t="str">
+        <x:v>2022SR0950122</x:v>
+      </x:c>
+      <x:c r="D60" s="9" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="E60" s="8" t="str">
+        <x:v>陈振宇</x:v>
+      </x:c>
+      <x:c r="F60" s="8" t="str">
+        <x:v>来源工作表：陈振宇；开发完成时间：2022-01-08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="42" customHeight="1">
+      <x:c r="A61" s="8" t="str">
+        <x:v>software-060</x:v>
+      </x:c>
+      <x:c r="B61" s="8" t="str">
+        <x:v>基于对抗变异的激光雷达点云数据扩增系统</x:v>
+      </x:c>
+      <x:c r="C61" s="8" t="str">
+        <x:v>2022SR0940055</x:v>
+      </x:c>
+      <x:c r="D61" s="9" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="E61" s="8" t="str">
+        <x:v>陈振宇</x:v>
+      </x:c>
+      <x:c r="F61" s="8" t="str">
+        <x:v>来源工作表：陈振宇；开发完成时间：2022-04-18</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/frontend/data-source/software-copyrights.xlsx
+++ b/frontend/data-source/software-copyrights.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="软件著作" sheetId="1" r:id="R8c2bca5133c54da4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="软件著作" sheetId="1" r:id="R22230f3a27674eba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1442,7 +1442,7 @@
         <x:v>2022</x:v>
       </x:c>
       <x:c r="E58" s="8" t="str">
-        <x:v>陈振宇</x:v>
+        <x:v>南京大学</x:v>
       </x:c>
       <x:c r="F58" s="8" t="str">
         <x:v>来源工作表：陈振宇；开发完成时间：2021-08-15</x:v>
@@ -1462,7 +1462,7 @@
         <x:v>2022</x:v>
       </x:c>
       <x:c r="E59" s="8" t="str">
-        <x:v>陈振宇</x:v>
+        <x:v>南京大学</x:v>
       </x:c>
       <x:c r="F59" s="8" t="str">
         <x:v>来源工作表：陈振宇；开发完成时间：2021-04-15</x:v>
@@ -1482,7 +1482,7 @@
         <x:v>2022</x:v>
       </x:c>
       <x:c r="E60" s="8" t="str">
-        <x:v>陈振宇</x:v>
+        <x:v>南京大学</x:v>
       </x:c>
       <x:c r="F60" s="8" t="str">
         <x:v>来源工作表：陈振宇；开发完成时间：2022-01-08</x:v>
@@ -1502,7 +1502,7 @@
         <x:v>2022</x:v>
       </x:c>
       <x:c r="E61" s="8" t="str">
-        <x:v>陈振宇</x:v>
+        <x:v>南京大学</x:v>
       </x:c>
       <x:c r="F61" s="8" t="str">
         <x:v>来源工作表：陈振宇；开发完成时间：2022-04-18</x:v>
